--- a/data/synth/review_sheet_batch3.xlsx
+++ b/data/synth/review_sheet_batch3.xlsx
@@ -441,7 +441,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>合成句審核表 — 請手語老師／聾人顧問逐句確認 Gloss 與 NMS （審核結果填：通過／修正／不通過；rule-derived 句型請優先審核）</t>
+          <t>合成句審核表 — 請手語老師／聾人顧問逐句確認 Gloss 與 NMS （審核結果填：通過／修正／不通過；rule-derived 句型請優先審核）｜審核結果欄為 AI 語言學預審（依文獻＋語料實證）；標『需母語者裁定/確認』者仍須手語老師逐句覆核，非母語聾人最終判定</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,6 @@
           <t>我/咖啡/喝/要</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>自有實例 S14 我要喝水→我/水/喝/要 之飲料槽位替換（規則1 情態句尾）；槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -539,9 +538,16 @@
           <t>咖啡</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,7 +575,6 @@
           <t>我/牛奶/喝/要</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>自有實例 S14 我要喝水→我/水/喝/要 之飲料槽位替換（規則1 情態句尾）；槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -580,9 +585,16 @@
           <t>牛奶</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -610,7 +622,6 @@
           <t>我/果汁/喝/要</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>自有實例 S14 我要喝水→我/水/喝/要 之飲料槽位替換（規則1 情態句尾）；槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -621,9 +632,16 @@
           <t>果汁</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,7 +669,6 @@
           <t>我/紅茶/喝/要</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>自有實例 S14 我要喝水→我/水/喝/要 之飲料槽位替換（規則1 情態句尾）；槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -662,9 +679,16 @@
           <t>紅茶</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -692,7 +716,6 @@
           <t>我/珍珠奶茶/喝/要</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>自有實例 S14 我要喝水→我/水/喝/要 之飲料槽位替換（規則1 情態句尾）；槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -703,9 +726,16 @@
           <t>珍珠奶茶</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -748,9 +778,16 @@
           <t>咖啡</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -793,9 +830,16 @@
           <t>牛奶</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -838,9 +882,16 @@
           <t>果汁</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -883,9 +934,16 @@
           <t>紅茶</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -928,9 +986,16 @@
           <t>珍珠奶茶</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -958,7 +1023,6 @@
           <t>我/水果/吃/要</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -969,9 +1033,16 @@
           <t>水果、吃</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -999,7 +1070,6 @@
           <t>我/蘋果/吃/要</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1010,9 +1080,16 @@
           <t>蘋果、吃</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1040,7 +1117,6 @@
           <t>我/香蕉/吃/要</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1051,9 +1127,16 @@
           <t>香蕉、吃</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1081,7 +1164,6 @@
           <t>我/麵包/吃/要</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1092,9 +1174,16 @@
           <t>麵包、吃</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1122,7 +1211,6 @@
           <t>我/蛋糕/吃/要</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1133,9 +1221,16 @@
           <t>蛋糕、吃</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1163,7 +1258,6 @@
           <t>我/早餐/吃/要</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1174,9 +1268,16 @@
           <t>早餐、吃</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1204,7 +1305,6 @@
           <t>我/便當/吃/要</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>S14 句型之動詞（喝→吃）與賓語槽位類推（規則1）；「吃」與槽位詞均取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1215,9 +1315,16 @@
           <t>便當、吃</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1260,9 +1367,16 @@
           <t>水果、吃</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1305,9 +1419,16 @@
           <t>蘋果、吃</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1350,9 +1471,16 @@
           <t>香蕉、吃</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1395,9 +1523,16 @@
           <t>麵包、吃</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1440,9 +1575,16 @@
           <t>蛋糕、吃</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1485,9 +1627,16 @@
           <t>早餐、吃</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1530,9 +1679,16 @@
           <t>便當、吃</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1560,7 +1716,6 @@
           <t>我/去/學校/要</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>T6 之場所槽位擴充（規則1）；「學校」見 Jane Tsay 2021 例句，槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1571,9 +1726,16 @@
           <t>學校</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1601,7 +1763,6 @@
           <t>我/去/醫院/要</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>T6 之場所槽位擴充（規則1）；「學校」見 Jane Tsay 2021 例句，槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1612,9 +1773,16 @@
           <t>醫院</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1642,7 +1810,6 @@
           <t>我/去/公車站/要</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>T6 之場所槽位擴充（規則1）；「學校」見 Jane Tsay 2021 例句，槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1653,9 +1820,16 @@
           <t>公車站</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1683,7 +1857,6 @@
           <t>我/去/火車站/要</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>T6 之場所槽位擴充（規則1）；「學校」見 Jane Tsay 2021 例句，槽位詞取自中正手語辭典，尚無自有影片，審核優先</t>
@@ -1694,9 +1867,16 @@
           <t>火車站</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 情態句尾符68%(傾向)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1739,9 +1919,16 @@
           <t>學校</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1784,9 +1971,16 @@
           <t>學校</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1829,9 +2023,16 @@
           <t>學校</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1874,9 +2075,16 @@
           <t>學校</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1919,9 +2127,16 @@
           <t>醫院</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1964,9 +2179,16 @@
           <t>醫院</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2009,9 +2231,16 @@
           <t>醫院</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2054,9 +2283,16 @@
           <t>醫院</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2099,9 +2335,16 @@
           <t>公車站</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2144,9 +2387,16 @@
           <t>公車站</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2189,9 +2439,16 @@
           <t>公車站</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2234,9 +2491,16 @@
           <t>公車站</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2279,9 +2543,16 @@
           <t>火車站</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2324,9 +2595,16 @@
           <t>火車站</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2369,9 +2647,16 @@
           <t>火車站</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2414,9 +2699,16 @@
           <t>火車站</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>語序符語料庫主流傾向，惟屬規則推導未經母語者裁定，需覆核；NMS需影片裁定</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>[AI語言學預審 2026-07-23] 否定句尾符語料庫76%；時間句首符82%；NMS形式/時間範圍非文字可定（陳怡君2012：不同疑問功能表情不同）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
